--- a/tabs/ZDATA__link_for_DBSW.xlsx
+++ b/tabs/ZDATA__link_for_DBSW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64a25058d50c5c4/OneD-2025/6_homepage_byungkiryu/byungkiryu/tabs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e64a25058d50c5c4/OneD-2026/6_homepage_byungkiryu/byungkiryu/tabs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="387" documentId="13_ncr:1_{17D0EB6A-8C48-4958-B4B1-97F25152412E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B5B6312-391C-43F9-8863-CD8B6AFDA21E}"/>
+  <xr:revisionPtr revIDLastSave="389" documentId="13_ncr:1_{17D0EB6A-8C48-4958-B4B1-97F25152412E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AE196AE-8B95-4D2A-90E0-8444CFDF862D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{6D651AE5-37C2-4486-97AE-FE18438EF94C}"/>
   </bookViews>
@@ -203,15 +203,15 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>https://tematdbv.streamlit.app/</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>Ultra-high quality thermoelectric material property database. Developed by Dr. Byungki Ryu. (v1.1.6)</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>teMatDb v1.1.4 (old)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://tematdb.streamlit.app/</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1108,10 +1108,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1515,10 +1511,10 @@
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="26.25" x14ac:dyDescent="0.6">
@@ -1526,7 +1522,7 @@
         <v>23</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>33</v>
